--- a/outputs/Payroll_Summary_2026-01.xlsx
+++ b/outputs/Payroll_Summary_2026-01.xlsx
@@ -691,7 +691,7 @@
         <v>6270</v>
       </c>
       <c r="F5" t="n">
-        <v>3232.21</v>
+        <v>3232.22</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>7680</v>
+        <v>7040</v>
       </c>
       <c r="F7" t="n">
         <v>1969.74</v>
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>9649.74</v>
+        <v>9009.74</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>9649.74</v>
+        <v>9009.74</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1920</v>
+        <v>2080</v>
       </c>
       <c r="F8" t="n">
         <v>194.22</v>
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2114.22</v>
+        <v>2274.22</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2114.22</v>
+        <v>2274.22</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>

--- a/outputs/Payroll_Summary_2026-01.xlsx
+++ b/outputs/Payroll_Summary_2026-01.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,77 +417,77 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>員工</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>全名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>工時</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>OT工時</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>底薪</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>總佣金</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>津貼</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>報銷</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>微調</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>出勤獎</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>總收入</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>MPF扣除</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>MPF狀態</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>實發薪資</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>地點</t>
         </is>
@@ -853,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2080</v>
+        <v>1920</v>
       </c>
       <c r="F8" t="n">
         <v>194.22</v>
@@ -871,7 +859,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2274.22</v>
+        <v>2114.22</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -882,7 +870,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2274.22</v>
+        <v>2114.22</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
